--- a/sources/ling_step8.xlsx
+++ b/sources/ling_step8.xlsx
@@ -425,7 +425,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -11383,22 +11383,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>(~B)RDS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11480,22 +11485,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>(~U)Quick roll to background; (~D)Quick roll to foreground</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12359,12 +12369,12 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -12446,7 +12456,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">

--- a/sources/ling_step8.xlsx
+++ b/sources/ling_step8.xlsx
@@ -1087,6 +1087,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -1154,6 +1159,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -1216,6 +1226,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1276,6 +1291,11 @@
       <c r="U12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -12661,6 +12681,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -12706,6 +12731,11 @@
       <c r="S150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
